--- a/mockdata/AMRFinderPlus_Results.xlsx
+++ b/mockdata/AMRFinderPlus_Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
   <si>
     <t>Isolate ID</t>
   </si>
@@ -19,13 +19,22 @@
     <t>Gene Symbol</t>
   </si>
   <si>
+    <t>Sequence Name</t>
+  </si>
+  <si>
     <t>Element Type</t>
   </si>
   <si>
-    <t>Resistance Class</t>
-  </si>
-  <si>
-    <t>Resistance Subclass</t>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Subclass</t>
+  </si>
+  <si>
+    <t>Target Length</t>
+  </si>
+  <si>
+    <t>Reference Length</t>
   </si>
   <si>
     <t>Identity %</t>
@@ -34,12 +43,21 @@
     <t>Coverage %</t>
   </si>
   <si>
+    <t>Alignment Length</t>
+  </si>
+  <si>
+    <t>Accession</t>
+  </si>
+  <si>
     <t>ISO-101</t>
   </si>
   <si>
     <t>bla</t>
   </si>
   <si>
+    <t>subclass B3 metallo-beta-lactamase</t>
+  </si>
+  <si>
     <t>AMR</t>
   </si>
   <si>
@@ -52,9 +70,15 @@
     <t>58.33</t>
   </si>
   <si>
+    <t>WP_122630833.1</t>
+  </si>
+  <si>
     <t>erm</t>
   </si>
   <si>
+    <t>23S rRNA methyltransferase Erm</t>
+  </si>
+  <si>
     <t>MACROLIDE</t>
   </si>
   <si>
@@ -64,12 +88,18 @@
     <t>39.76</t>
   </si>
   <si>
+    <t>WP_015345217.1</t>
+  </si>
+  <si>
     <t>ISO-102</t>
   </si>
   <si>
     <t>aac(3)-I</t>
   </si>
   <si>
+    <t>AAC(3)-I aminoglycoside</t>
+  </si>
+  <si>
     <t>AMINOGLYCOSIDE</t>
   </si>
   <si>
@@ -82,12 +112,18 @@
     <t>62.00</t>
   </si>
   <si>
+    <t>ABL71428.1</t>
+  </si>
+  <si>
     <t>ISO-103</t>
   </si>
   <si>
     <t>arsN1</t>
   </si>
   <si>
+    <t>arsinothricin N-acetyltransferase</t>
+  </si>
+  <si>
     <t>STRESS</t>
   </si>
   <si>
@@ -101,6 +137,9 @@
   </si>
   <si>
     <t>51.48</t>
+  </si>
+  <si>
+    <t>AAN67541.1</t>
   </si>
 </sst>
 </file>
@@ -122,6 +161,11 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="12"/>
       <color indexed="9"/>
@@ -132,14 +176,8 @@
       <color indexed="9"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,109 +190,13 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -278,50 +220,29 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -344,8 +265,6 @@
       <rgbColor rgb="ff1f1f1f"/>
       <rgbColor rgb="ffefefef"/>
       <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffdbdbdb"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -362,10 +281,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -542,11 +461,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -555,33 +477,33 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
-          <a:lnSpc>
-            <a:spcPct val="100000"/>
-          </a:lnSpc>
-          <a:spcBef>
-            <a:spcPts val="0"/>
-          </a:spcBef>
-          <a:spcAft>
-            <a:spcPts val="0"/>
-          </a:spcAft>
-          <a:buClrTx/>
-          <a:buSzTx/>
-          <a:buFontTx/>
-          <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -820,12 +742,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1106,7 +1028,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1374,11 +1296,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="13" width="16.3516" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="60.55" customHeight="1">
@@ -1403,383 +1325,477 @@
       <c r="G1" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="H1" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s" s="2">
+        <v>11</v>
+      </c>
       <c r="M1" s="3"/>
-    </row>
-    <row r="2" ht="46.55" customHeight="1">
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+    </row>
+    <row r="2" ht="74.55" customHeight="1">
       <c r="A2" t="s" s="4">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s" s="5">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s" s="6">
         <v>12</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="B2" t="s" s="4">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s" s="4">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5">
+        <v>278</v>
+      </c>
+      <c r="H2" s="5">
+        <v>295</v>
+      </c>
+      <c r="I2" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="K2" s="5">
+        <v>240</v>
+      </c>
+      <c r="L2" t="s" s="4">
+        <v>19</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="8">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s" s="9">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s" s="10">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s" s="10">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s" s="10">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s" s="10">
+      <c r="A3" t="s" s="4">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="G3" t="s" s="10">
-        <v>16</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
+      <c r="E3" t="s" s="4">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s" s="4">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5">
+        <v>271</v>
+      </c>
+      <c r="H3" s="5">
+        <v>281</v>
+      </c>
+      <c r="I3" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="K3" s="5">
+        <v>249</v>
+      </c>
+      <c r="L3" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="8">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s" s="9">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s" s="10">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s" s="10">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s" s="10">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s" s="10">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s" s="10">
-        <v>22</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="A4" t="s" s="4">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s" s="4">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s" s="4">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="5">
+        <v>196</v>
+      </c>
+      <c r="H4" s="5">
+        <v>152</v>
+      </c>
+      <c r="I4" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="K4" s="5">
+        <v>150</v>
+      </c>
+      <c r="L4" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" t="s" s="8">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s" s="9">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s" s="10">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s" s="10">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s" s="10">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s" s="10">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s" s="10">
-        <v>29</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="A5" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5">
+        <v>202</v>
+      </c>
+      <c r="H5" s="5">
+        <v>186</v>
+      </c>
+      <c r="I5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="K5" s="5">
+        <v>155</v>
+      </c>
+      <c r="L5" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
     <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>

--- a/mockdata/AMRFinderPlus_Results.xlsx
+++ b/mockdata/AMRFinderPlus_Results.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taylorlaurensergel/Desktop/Honours 26'/IMY/Project/IMY772Project/mockdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDD1FB7-36A0-7E44-A42E-A523FE7B755F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="15100" yWindow="660" windowWidth="15140" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="129">
   <si>
     <t>Isolate ID</t>
   </si>
@@ -140,41 +149,288 @@
   </si>
   <si>
     <t>AAN67541.1</t>
+  </si>
+  <si>
+    <t>ISO-104</t>
+  </si>
+  <si>
+    <t>ISO-105</t>
+  </si>
+  <si>
+    <t>ISO-106</t>
+  </si>
+  <si>
+    <t>ISO-107</t>
+  </si>
+  <si>
+    <t>ISO-108</t>
+  </si>
+  <si>
+    <t>ISO-109</t>
+  </si>
+  <si>
+    <t>ISO-110</t>
+  </si>
+  <si>
+    <t>ISO-111</t>
+  </si>
+  <si>
+    <t>ISO-112</t>
+  </si>
+  <si>
+    <t>ISO-113</t>
+  </si>
+  <si>
+    <t>ISO-114</t>
+  </si>
+  <si>
+    <t>ISO-115</t>
+  </si>
+  <si>
+    <t>ISO-116</t>
+  </si>
+  <si>
+    <t>ISO-117</t>
+  </si>
+  <si>
+    <t>ISO-118</t>
+  </si>
+  <si>
+    <t>ISO-119</t>
+  </si>
+  <si>
+    <t>ISO-120</t>
+  </si>
+  <si>
+    <t>ISO-121</t>
+  </si>
+  <si>
+    <t>ISO-122</t>
+  </si>
+  <si>
+    <t>ISO-123</t>
+  </si>
+  <si>
+    <t>ISO-124</t>
+  </si>
+  <si>
+    <t>ISO-125</t>
+  </si>
+  <si>
+    <t>ISO-126</t>
+  </si>
+  <si>
+    <t>ISO-127</t>
+  </si>
+  <si>
+    <t>ISO-128</t>
+  </si>
+  <si>
+    <t>ISO-129</t>
+  </si>
+  <si>
+    <t>ISO-130</t>
+  </si>
+  <si>
+    <t>ISO-131</t>
+  </si>
+  <si>
+    <t>ISO-132</t>
+  </si>
+  <si>
+    <t>ISO-133</t>
+  </si>
+  <si>
+    <t>ISO-134</t>
+  </si>
+  <si>
+    <t>ISO-135</t>
+  </si>
+  <si>
+    <t>ISO-136</t>
+  </si>
+  <si>
+    <t>ISO-137</t>
+  </si>
+  <si>
+    <t>ISO-138</t>
+  </si>
+  <si>
+    <t>ISO-139</t>
+  </si>
+  <si>
+    <t>ISO-140</t>
+  </si>
+  <si>
+    <t>ISO-141</t>
+  </si>
+  <si>
+    <t>ISO-142</t>
+  </si>
+  <si>
+    <t>ISO-143</t>
+  </si>
+  <si>
+    <t>ISO-144</t>
+  </si>
+  <si>
+    <t>ISO-145</t>
+  </si>
+  <si>
+    <t>ISO-146</t>
+  </si>
+  <si>
+    <t>aph(3')-Ia</t>
+  </si>
+  <si>
+    <t>aminoglycoside phosphotransferase</t>
+  </si>
+  <si>
+    <t>KANAMYCIN</t>
+  </si>
+  <si>
+    <t>WP_000027057.1</t>
+  </si>
+  <si>
+    <t>sul2</t>
+  </si>
+  <si>
+    <t>dihydropteroate synthase Sul2</t>
+  </si>
+  <si>
+    <t>SULFONAMIDE</t>
+  </si>
+  <si>
+    <t>dfrA1</t>
+  </si>
+  <si>
+    <t>dihydrofolate reductase DfrA1</t>
+  </si>
+  <si>
+    <t>TRIMETHOPRIM</t>
+  </si>
+  <si>
+    <t>WP_063855648.1</t>
+  </si>
+  <si>
+    <t>sul1</t>
+  </si>
+  <si>
+    <t>dihydropteroate synthase Sul1</t>
+  </si>
+  <si>
+    <t>blaTEM-1</t>
+  </si>
+  <si>
+    <t>TEM-1 beta-lactamase</t>
+  </si>
+  <si>
+    <t>AMPICILLIN</t>
+  </si>
+  <si>
+    <t>WP_001082289.1</t>
+  </si>
+  <si>
+    <t>WP_001134315.1</t>
+  </si>
+  <si>
+    <t>blaOXA-48</t>
+  </si>
+  <si>
+    <t>OXA-48 carbapenemase</t>
+  </si>
+  <si>
+    <t>CARBAPENEM</t>
+  </si>
+  <si>
+    <t>WP_001213570.1</t>
+  </si>
+  <si>
+    <t>blaCTX-M</t>
+  </si>
+  <si>
+    <t>CTX-M extended-spectrum beta-lactamase</t>
+  </si>
+  <si>
+    <t>CEPHALOSPORIN</t>
+  </si>
+  <si>
+    <t>mcr-1</t>
+  </si>
+  <si>
+    <t>phosphoethanolamine transferase MCR-1</t>
+  </si>
+  <si>
+    <t>COLISTIN</t>
+  </si>
+  <si>
+    <t>blaNDM-1</t>
+  </si>
+  <si>
+    <t>New Delhi metallo-beta-lactamase</t>
+  </si>
+  <si>
+    <t>WP_000543430.1</t>
+  </si>
+  <si>
+    <t>WP_063855649.1</t>
+  </si>
+  <si>
+    <t>catA1</t>
+  </si>
+  <si>
+    <t>chloramphenicol acetyltransferase CatA1</t>
+  </si>
+  <si>
+    <t>PHENICOL</t>
+  </si>
+  <si>
+    <t>CHLORAMPHENICOL</t>
+  </si>
+  <si>
+    <t>qnrS</t>
+  </si>
+  <si>
+    <t>quinolone resistance protein QnrS</t>
+  </si>
+  <si>
+    <t>QUINOLONE</t>
+  </si>
+  <si>
+    <t>CIPROFLOXACIN</t>
+  </si>
+  <si>
+    <t>tetA</t>
+  </si>
+  <si>
+    <t>tetracycline efflux pump TetA</t>
+  </si>
+  <si>
+    <t>TETRACYCLINE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -216,33 +472,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -253,25 +509,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff1f1f1f"/>
-      <rgbColor rgb="ffefefef"/>
-      <rgbColor rgb="ffa5a5a5"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF1F1F1F"/>
+      <rgbColor rgb="FFEFEFEF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -473,7 +789,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -491,7 +807,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -520,7 +836,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -545,7 +861,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -570,7 +886,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -595,7 +911,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -620,7 +936,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -645,7 +961,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -670,7 +986,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -695,7 +1011,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -720,7 +1036,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -733,9 +1049,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -752,7 +1074,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -770,7 +1092,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -795,7 +1117,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -820,7 +1142,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -845,7 +1167,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -870,7 +1192,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -895,7 +1217,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -920,7 +1242,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -945,7 +1267,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -970,7 +1292,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -995,7 +1317,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1008,9 +1330,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1024,7 +1352,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1042,7 +1370,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1071,7 +1399,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1096,7 +1424,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1121,7 +1449,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1146,7 +1474,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1171,7 +1499,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1196,7 +1524,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1221,7 +1549,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1246,7 +1574,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1271,7 +1599,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1284,83 +1612,91 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O107"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="46.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="16.33203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="2">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="2">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="2">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" ht="74.55" customHeight="1">
-      <c r="A2" t="s" s="4">
+    <row r="2" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s" s="4">
+      <c r="B2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s" s="4">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s" s="4">
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s" s="4">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="5">
@@ -1369,39 +1705,39 @@
       <c r="H2" s="5">
         <v>295</v>
       </c>
-      <c r="I2" t="s" s="4">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s" s="4">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K2" s="5">
         <v>240</v>
       </c>
-      <c r="L2" t="s" s="4">
+      <c r="L2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="4">
+    <row r="3" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s" s="4">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s" s="4">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s" s="4">
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s" s="4">
+      <c r="F3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="5">
@@ -1410,39 +1746,39 @@
       <c r="H3" s="5">
         <v>281</v>
       </c>
-      <c r="I3" t="s" s="4">
+      <c r="I3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s" s="4">
+      <c r="J3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="K3" s="5">
         <v>249</v>
       </c>
-      <c r="L3" t="s" s="4">
+      <c r="L3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="4">
+    <row r="4" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s" s="4">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s" s="4">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s" s="4">
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s" s="4">
+      <c r="F4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="5">
@@ -1451,39 +1787,39 @@
       <c r="H4" s="5">
         <v>152</v>
       </c>
-      <c r="I4" t="s" s="4">
+      <c r="I4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s" s="4">
+      <c r="J4" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K4" s="5">
         <v>150</v>
       </c>
-      <c r="L4" t="s" s="4">
+      <c r="L4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" t="s" s="4">
+    <row r="5" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s" s="4">
+      <c r="B5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C5" t="s" s="4">
+      <c r="C5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s" s="4">
+      <c r="D5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E5" t="s" s="4">
+      <c r="E5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s" s="4">
+      <c r="F5" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G5" s="5">
@@ -1492,314 +1828,3952 @@
       <c r="H5" s="5">
         <v>186</v>
       </c>
-      <c r="I5" t="s" s="4">
+      <c r="I5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J5" t="s" s="4">
+      <c r="J5" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="5">
         <v>155</v>
       </c>
-      <c r="L5" t="s" s="4">
+      <c r="L5" s="4" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+    <row r="6" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="5">
+        <v>349</v>
+      </c>
+      <c r="H6" s="5">
+        <v>316</v>
+      </c>
+      <c r="I6" s="4">
+        <v>93.86</v>
+      </c>
+      <c r="J6" s="4">
+        <v>96.72</v>
+      </c>
+      <c r="K6" s="5">
+        <v>130</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+    <row r="7" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="5">
+        <v>155</v>
+      </c>
+      <c r="H7" s="5">
+        <v>309</v>
+      </c>
+      <c r="I7" s="4">
+        <v>80.959999999999994</v>
+      </c>
+      <c r="J7" s="4">
+        <v>65.78</v>
+      </c>
+      <c r="K7" s="5">
+        <v>129</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+    <row r="8" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="5">
+        <v>215</v>
+      </c>
+      <c r="H8" s="5">
+        <v>346</v>
+      </c>
+      <c r="I8" s="4">
+        <v>79.19</v>
+      </c>
+      <c r="J8" s="4">
+        <v>74.47</v>
+      </c>
+      <c r="K8" s="5">
+        <v>167</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+    <row r="9" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="5">
+        <v>349</v>
+      </c>
+      <c r="H9" s="5">
+        <v>191</v>
+      </c>
+      <c r="I9" s="4">
+        <v>77.7</v>
+      </c>
+      <c r="J9" s="4">
+        <v>36.67</v>
+      </c>
+      <c r="K9" s="5">
+        <v>159</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+    <row r="10" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="5">
+        <v>301</v>
+      </c>
+      <c r="H10" s="5">
+        <v>326</v>
+      </c>
+      <c r="I10" s="4">
+        <v>81.069999999999993</v>
+      </c>
+      <c r="J10" s="4">
+        <v>80.319999999999993</v>
+      </c>
+      <c r="K10" s="5">
+        <v>280</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+    <row r="11" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="5">
+        <v>325</v>
+      </c>
+      <c r="H11" s="5">
+        <v>303</v>
+      </c>
+      <c r="I11" s="4">
+        <v>94.91</v>
+      </c>
+      <c r="J11" s="4">
+        <v>71.790000000000006</v>
+      </c>
+      <c r="K11" s="5">
+        <v>150</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+    <row r="12" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="5">
+        <v>238</v>
+      </c>
+      <c r="H12" s="5">
+        <v>286</v>
+      </c>
+      <c r="I12" s="4">
+        <v>91.54</v>
+      </c>
+      <c r="J12" s="4">
+        <v>39.479999999999997</v>
+      </c>
+      <c r="K12" s="5">
+        <v>174</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+    <row r="13" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="5">
+        <v>153</v>
+      </c>
+      <c r="H13" s="5">
+        <v>257</v>
+      </c>
+      <c r="I13" s="4">
+        <v>77.64</v>
+      </c>
+      <c r="J13" s="4">
+        <v>97.45</v>
+      </c>
+      <c r="K13" s="5">
+        <v>151</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+    <row r="14" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="5">
+        <v>337</v>
+      </c>
+      <c r="H14" s="5">
+        <v>283</v>
+      </c>
+      <c r="I14" s="4">
+        <v>90.4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>94.78</v>
+      </c>
+      <c r="K14" s="5">
+        <v>189</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+    <row r="15" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="5">
+        <v>269</v>
+      </c>
+      <c r="H15" s="5">
+        <v>261</v>
+      </c>
+      <c r="I15" s="4">
+        <v>83.06</v>
+      </c>
+      <c r="J15" s="4">
+        <v>50.96</v>
+      </c>
+      <c r="K15" s="5">
+        <v>188</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+    <row r="16" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="5">
+        <v>342</v>
+      </c>
+      <c r="H16" s="5">
+        <v>268</v>
+      </c>
+      <c r="I16" s="4">
+        <v>90.26</v>
+      </c>
+      <c r="J16" s="4">
+        <v>59.63</v>
+      </c>
+      <c r="K16" s="5">
+        <v>265</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+    <row r="17" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="5">
+        <v>276</v>
+      </c>
+      <c r="H17" s="5">
+        <v>233</v>
+      </c>
+      <c r="I17" s="4">
+        <v>87.19</v>
+      </c>
+      <c r="J17" s="4">
+        <v>58.06</v>
+      </c>
+      <c r="K17" s="5">
+        <v>143</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+    <row r="18" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="5">
+        <v>237</v>
+      </c>
+      <c r="H18" s="5">
+        <v>221</v>
+      </c>
+      <c r="I18" s="4">
+        <v>92.53</v>
+      </c>
+      <c r="J18" s="4">
+        <v>52.96</v>
+      </c>
+      <c r="K18" s="5">
+        <v>196</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
+    <row r="19" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="5">
+        <v>334</v>
+      </c>
+      <c r="H19" s="5">
+        <v>254</v>
+      </c>
+      <c r="I19" s="4">
+        <v>88.88</v>
+      </c>
+      <c r="J19" s="4">
+        <v>50.62</v>
+      </c>
+      <c r="K19" s="5">
+        <v>245</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+    <row r="20" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="5">
+        <v>315</v>
+      </c>
+      <c r="H20" s="5">
+        <v>332</v>
+      </c>
+      <c r="I20" s="4">
+        <v>86.2</v>
+      </c>
+      <c r="J20" s="4">
+        <v>36.119999999999997</v>
+      </c>
+      <c r="K20" s="5">
+        <v>245</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+    <row r="21" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="5">
+        <v>212</v>
+      </c>
+      <c r="H21" s="5">
+        <v>228</v>
+      </c>
+      <c r="I21" s="4">
+        <v>89.54</v>
+      </c>
+      <c r="J21" s="4">
+        <v>65.760000000000005</v>
+      </c>
+      <c r="K21" s="5">
+        <v>204</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+    <row r="22" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="5">
+        <v>238</v>
+      </c>
+      <c r="H22" s="5">
+        <v>258</v>
+      </c>
+      <c r="I22" s="4">
+        <v>88.76</v>
+      </c>
+      <c r="J22" s="4">
+        <v>57.87</v>
+      </c>
+      <c r="K22" s="5">
+        <v>215</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
     </row>
+    <row r="23" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="5">
+        <v>180</v>
+      </c>
+      <c r="H23" s="5">
+        <v>334</v>
+      </c>
+      <c r="I23" s="4">
+        <v>82.89</v>
+      </c>
+      <c r="J23" s="4">
+        <v>83.29</v>
+      </c>
+      <c r="K23" s="5">
+        <v>132</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="5">
+        <v>199</v>
+      </c>
+      <c r="H24" s="5">
+        <v>205</v>
+      </c>
+      <c r="I24" s="4">
+        <v>81.91</v>
+      </c>
+      <c r="J24" s="4">
+        <v>73.319999999999993</v>
+      </c>
+      <c r="K24" s="5">
+        <v>181</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="5">
+        <v>302</v>
+      </c>
+      <c r="H25" s="5">
+        <v>222</v>
+      </c>
+      <c r="I25" s="4">
+        <v>95.82</v>
+      </c>
+      <c r="J25" s="4">
+        <v>54.26</v>
+      </c>
+      <c r="K25" s="5">
+        <v>132</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="5">
+        <v>331</v>
+      </c>
+      <c r="H26" s="5">
+        <v>286</v>
+      </c>
+      <c r="I26" s="4">
+        <v>81.86</v>
+      </c>
+      <c r="J26" s="4">
+        <v>98.33</v>
+      </c>
+      <c r="K26" s="5">
+        <v>152</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="5">
+        <v>224</v>
+      </c>
+      <c r="H27" s="5">
+        <v>328</v>
+      </c>
+      <c r="I27" s="4">
+        <v>90.95</v>
+      </c>
+      <c r="J27" s="4">
+        <v>83.93</v>
+      </c>
+      <c r="K27" s="5">
+        <v>136</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="5">
+        <v>222</v>
+      </c>
+      <c r="H28" s="5">
+        <v>270</v>
+      </c>
+      <c r="I28" s="4">
+        <v>86.01</v>
+      </c>
+      <c r="J28" s="4">
+        <v>46.98</v>
+      </c>
+      <c r="K28" s="5">
+        <v>181</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="5">
+        <v>166</v>
+      </c>
+      <c r="H29" s="5">
+        <v>252</v>
+      </c>
+      <c r="I29" s="4">
+        <v>76.849999999999994</v>
+      </c>
+      <c r="J29" s="4">
+        <v>75.91</v>
+      </c>
+      <c r="K29" s="5">
+        <v>151</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="5">
+        <v>188</v>
+      </c>
+      <c r="H30" s="5">
+        <v>188</v>
+      </c>
+      <c r="I30" s="4">
+        <v>77.13</v>
+      </c>
+      <c r="J30" s="4">
+        <v>51.13</v>
+      </c>
+      <c r="K30" s="5">
+        <v>158</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="5">
+        <v>345</v>
+      </c>
+      <c r="H31" s="5">
+        <v>256</v>
+      </c>
+      <c r="I31" s="4">
+        <v>94.39</v>
+      </c>
+      <c r="J31" s="4">
+        <v>59.72</v>
+      </c>
+      <c r="K31" s="5">
+        <v>177</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="5">
+        <v>228</v>
+      </c>
+      <c r="H32" s="5">
+        <v>295</v>
+      </c>
+      <c r="I32" s="4">
+        <v>76.510000000000005</v>
+      </c>
+      <c r="J32" s="4">
+        <v>97.41</v>
+      </c>
+      <c r="K32" s="5">
+        <v>199</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="5">
+        <v>345</v>
+      </c>
+      <c r="H33" s="5">
+        <v>203</v>
+      </c>
+      <c r="I33" s="4">
+        <v>80.28</v>
+      </c>
+      <c r="J33" s="4">
+        <v>77.930000000000007</v>
+      </c>
+      <c r="K33" s="5">
+        <v>200</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="5">
+        <v>211</v>
+      </c>
+      <c r="H34" s="5">
+        <v>194</v>
+      </c>
+      <c r="I34" s="4">
+        <v>76.88</v>
+      </c>
+      <c r="J34" s="4">
+        <v>35.17</v>
+      </c>
+      <c r="K34" s="5">
+        <v>190</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="5">
+        <v>330</v>
+      </c>
+      <c r="H35" s="5">
+        <v>222</v>
+      </c>
+      <c r="I35" s="4">
+        <v>96.49</v>
+      </c>
+      <c r="J35" s="4">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="K35" s="5">
+        <v>209</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="5">
+        <v>217</v>
+      </c>
+      <c r="H36" s="5">
+        <v>310</v>
+      </c>
+      <c r="I36" s="4">
+        <v>91.53</v>
+      </c>
+      <c r="J36" s="4">
+        <v>95.69</v>
+      </c>
+      <c r="K36" s="5">
+        <v>195</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="5">
+        <v>179</v>
+      </c>
+      <c r="H37" s="5">
+        <v>289</v>
+      </c>
+      <c r="I37" s="4">
+        <v>91.19</v>
+      </c>
+      <c r="J37" s="4">
+        <v>94.05</v>
+      </c>
+      <c r="K37" s="5">
+        <v>134</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="5">
+        <v>168</v>
+      </c>
+      <c r="H38" s="5">
+        <v>165</v>
+      </c>
+      <c r="I38" s="4">
+        <v>94.82</v>
+      </c>
+      <c r="J38" s="4">
+        <v>73.680000000000007</v>
+      </c>
+      <c r="K38" s="5">
+        <v>130</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="5">
+        <v>326</v>
+      </c>
+      <c r="H39" s="5">
+        <v>227</v>
+      </c>
+      <c r="I39" s="4">
+        <v>85.06</v>
+      </c>
+      <c r="J39" s="4">
+        <v>52.7</v>
+      </c>
+      <c r="K39" s="5">
+        <v>209</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="5">
+        <v>276</v>
+      </c>
+      <c r="H40" s="5">
+        <v>262</v>
+      </c>
+      <c r="I40" s="4">
+        <v>89.95</v>
+      </c>
+      <c r="J40" s="4">
+        <v>92.81</v>
+      </c>
+      <c r="K40" s="5">
+        <v>140</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="5">
+        <v>304</v>
+      </c>
+      <c r="H41" s="5">
+        <v>214</v>
+      </c>
+      <c r="I41" s="4">
+        <v>77.28</v>
+      </c>
+      <c r="J41" s="4">
+        <v>97.52</v>
+      </c>
+      <c r="K41" s="5">
+        <v>123</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="5">
+        <v>322</v>
+      </c>
+      <c r="H42" s="5">
+        <v>218</v>
+      </c>
+      <c r="I42" s="4">
+        <v>76.010000000000005</v>
+      </c>
+      <c r="J42" s="4">
+        <v>84.16</v>
+      </c>
+      <c r="K42" s="5">
+        <v>193</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G43" s="5">
+        <v>261</v>
+      </c>
+      <c r="H43" s="5">
+        <v>312</v>
+      </c>
+      <c r="I43" s="4">
+        <v>99.23</v>
+      </c>
+      <c r="J43" s="4">
+        <v>65.55</v>
+      </c>
+      <c r="K43" s="5">
+        <v>245</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="5">
+        <v>235</v>
+      </c>
+      <c r="H44" s="5">
+        <v>232</v>
+      </c>
+      <c r="I44" s="4">
+        <v>77.61</v>
+      </c>
+      <c r="J44" s="4">
+        <v>45.45</v>
+      </c>
+      <c r="K44" s="5">
+        <v>205</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="5">
+        <v>327</v>
+      </c>
+      <c r="H45" s="5">
+        <v>276</v>
+      </c>
+      <c r="I45" s="4">
+        <v>91.56</v>
+      </c>
+      <c r="J45" s="4">
+        <v>61.03</v>
+      </c>
+      <c r="K45" s="5">
+        <v>193</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G46" s="5">
+        <v>159</v>
+      </c>
+      <c r="H46" s="5">
+        <v>266</v>
+      </c>
+      <c r="I46" s="4">
+        <v>82.86</v>
+      </c>
+      <c r="J46" s="4">
+        <v>56.01</v>
+      </c>
+      <c r="K46" s="5">
+        <v>125</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="5">
+        <v>288</v>
+      </c>
+      <c r="H47" s="5">
+        <v>268</v>
+      </c>
+      <c r="I47" s="4">
+        <v>76.36</v>
+      </c>
+      <c r="J47" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="K47" s="5">
+        <v>225</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G48" s="5">
+        <v>202</v>
+      </c>
+      <c r="H48" s="5">
+        <v>218</v>
+      </c>
+      <c r="I48" s="4">
+        <v>78.28</v>
+      </c>
+      <c r="J48" s="4">
+        <v>53.72</v>
+      </c>
+      <c r="K48" s="5">
+        <v>190</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G49" s="5">
+        <v>181</v>
+      </c>
+      <c r="H49" s="5">
+        <v>157</v>
+      </c>
+      <c r="I49" s="4">
+        <v>92.74</v>
+      </c>
+      <c r="J49" s="4">
+        <v>55.2</v>
+      </c>
+      <c r="K49" s="5">
+        <v>135</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G50" s="5">
+        <v>291</v>
+      </c>
+      <c r="H50" s="5">
+        <v>254</v>
+      </c>
+      <c r="I50" s="4">
+        <v>80.62</v>
+      </c>
+      <c r="J50" s="4">
+        <v>89.69</v>
+      </c>
+      <c r="K50" s="5">
+        <v>143</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="5">
+        <v>268</v>
+      </c>
+      <c r="H51" s="5">
+        <v>180</v>
+      </c>
+      <c r="I51" s="4">
+        <v>95.8</v>
+      </c>
+      <c r="J51" s="4">
+        <v>67.39</v>
+      </c>
+      <c r="K51" s="5">
+        <v>161</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" s="5">
+        <v>270</v>
+      </c>
+      <c r="H52" s="5">
+        <v>212</v>
+      </c>
+      <c r="I52" s="4">
+        <v>88.78</v>
+      </c>
+      <c r="J52" s="4">
+        <v>59.93</v>
+      </c>
+      <c r="K52" s="5">
+        <v>178</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G53" s="5">
+        <v>280</v>
+      </c>
+      <c r="H53" s="5">
+        <v>341</v>
+      </c>
+      <c r="I53" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="J53" s="4">
+        <v>52.96</v>
+      </c>
+      <c r="K53" s="5">
+        <v>154</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="5">
+        <v>237</v>
+      </c>
+      <c r="H54" s="5">
+        <v>279</v>
+      </c>
+      <c r="I54" s="4">
+        <v>95.51</v>
+      </c>
+      <c r="J54" s="4">
+        <v>53.38</v>
+      </c>
+      <c r="K54" s="5">
+        <v>154</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G55" s="5">
+        <v>273</v>
+      </c>
+      <c r="H55" s="5">
+        <v>238</v>
+      </c>
+      <c r="I55" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="J55" s="4">
+        <v>70.319999999999993</v>
+      </c>
+      <c r="K55" s="5">
+        <v>162</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" s="5">
+        <v>232</v>
+      </c>
+      <c r="H56" s="5">
+        <v>198</v>
+      </c>
+      <c r="I56" s="4">
+        <v>89.29</v>
+      </c>
+      <c r="J56" s="4">
+        <v>50.18</v>
+      </c>
+      <c r="K56" s="5">
+        <v>150</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="5">
+        <v>161</v>
+      </c>
+      <c r="H57" s="5">
+        <v>231</v>
+      </c>
+      <c r="I57" s="4">
+        <v>92.63</v>
+      </c>
+      <c r="J57" s="4">
+        <v>87.74</v>
+      </c>
+      <c r="K57" s="5">
+        <v>150</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G58" s="5">
+        <v>319</v>
+      </c>
+      <c r="H58" s="5">
+        <v>316</v>
+      </c>
+      <c r="I58" s="4">
+        <v>87.38</v>
+      </c>
+      <c r="J58" s="4">
+        <v>37.409999999999997</v>
+      </c>
+      <c r="K58" s="5">
+        <v>158</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G59" s="5">
+        <v>175</v>
+      </c>
+      <c r="H59" s="5">
+        <v>284</v>
+      </c>
+      <c r="I59" s="4">
+        <v>75.38</v>
+      </c>
+      <c r="J59" s="4">
+        <v>44.37</v>
+      </c>
+      <c r="K59" s="5">
+        <v>149</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="5">
+        <v>169</v>
+      </c>
+      <c r="H60" s="5">
+        <v>270</v>
+      </c>
+      <c r="I60" s="4">
+        <v>83.46</v>
+      </c>
+      <c r="J60" s="4">
+        <v>80.03</v>
+      </c>
+      <c r="K60" s="5">
+        <v>136</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="5">
+        <v>234</v>
+      </c>
+      <c r="H61" s="5">
+        <v>322</v>
+      </c>
+      <c r="I61" s="4">
+        <v>88.34</v>
+      </c>
+      <c r="J61" s="4">
+        <v>97.02</v>
+      </c>
+      <c r="K61" s="5">
+        <v>229</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G62" s="5">
+        <v>167</v>
+      </c>
+      <c r="H62" s="5">
+        <v>210</v>
+      </c>
+      <c r="I62" s="4">
+        <v>92.11</v>
+      </c>
+      <c r="J62" s="4">
+        <v>53.68</v>
+      </c>
+      <c r="K62" s="5">
+        <v>160</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G63" s="5">
+        <v>175</v>
+      </c>
+      <c r="H63" s="5">
+        <v>344</v>
+      </c>
+      <c r="I63" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="J63" s="4">
+        <v>41.53</v>
+      </c>
+      <c r="K63" s="5">
+        <v>160</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G64" s="5">
+        <v>233</v>
+      </c>
+      <c r="H64" s="5">
+        <v>164</v>
+      </c>
+      <c r="I64" s="4">
+        <v>83.96</v>
+      </c>
+      <c r="J64" s="4">
+        <v>62.99</v>
+      </c>
+      <c r="K64" s="5">
+        <v>138</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="5">
+        <v>285</v>
+      </c>
+      <c r="H65" s="5">
+        <v>255</v>
+      </c>
+      <c r="I65" s="4">
+        <v>79.25</v>
+      </c>
+      <c r="J65" s="4">
+        <v>40.130000000000003</v>
+      </c>
+      <c r="K65" s="5">
+        <v>166</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G66" s="5">
+        <v>308</v>
+      </c>
+      <c r="H66" s="5">
+        <v>324</v>
+      </c>
+      <c r="I66" s="4">
+        <v>87.44</v>
+      </c>
+      <c r="J66" s="4">
+        <v>72.91</v>
+      </c>
+      <c r="K66" s="5">
+        <v>181</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G67" s="5">
+        <v>320</v>
+      </c>
+      <c r="H67" s="5">
+        <v>152</v>
+      </c>
+      <c r="I67" s="4">
+        <v>97.53</v>
+      </c>
+      <c r="J67" s="4">
+        <v>79.040000000000006</v>
+      </c>
+      <c r="K67" s="5">
+        <v>149</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" s="5">
+        <v>168</v>
+      </c>
+      <c r="H68" s="5">
+        <v>263</v>
+      </c>
+      <c r="I68" s="4">
+        <v>99.69</v>
+      </c>
+      <c r="J68" s="4">
+        <v>54.45</v>
+      </c>
+      <c r="K68" s="5">
+        <v>142</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G69" s="5">
+        <v>326</v>
+      </c>
+      <c r="H69" s="5">
+        <v>214</v>
+      </c>
+      <c r="I69" s="4">
+        <v>96.13</v>
+      </c>
+      <c r="J69" s="4">
+        <v>47.95</v>
+      </c>
+      <c r="K69" s="5">
+        <v>178</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G70" s="5">
+        <v>273</v>
+      </c>
+      <c r="H70" s="5">
+        <v>177</v>
+      </c>
+      <c r="I70" s="4">
+        <v>84.53</v>
+      </c>
+      <c r="J70" s="4">
+        <v>58.33</v>
+      </c>
+      <c r="K70" s="5">
+        <v>135</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G71" s="5">
+        <v>211</v>
+      </c>
+      <c r="H71" s="5">
+        <v>199</v>
+      </c>
+      <c r="I71" s="4">
+        <v>82.31</v>
+      </c>
+      <c r="J71" s="4">
+        <v>96.95</v>
+      </c>
+      <c r="K71" s="5">
+        <v>134</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G72" s="5">
+        <v>210</v>
+      </c>
+      <c r="H72" s="5">
+        <v>187</v>
+      </c>
+      <c r="I72" s="4">
+        <v>75.06</v>
+      </c>
+      <c r="J72" s="4">
+        <v>53.2</v>
+      </c>
+      <c r="K72" s="5">
+        <v>184</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G73" s="5">
+        <v>232</v>
+      </c>
+      <c r="H73" s="5">
+        <v>180</v>
+      </c>
+      <c r="I73" s="4">
+        <v>88.77</v>
+      </c>
+      <c r="J73" s="4">
+        <v>51.92</v>
+      </c>
+      <c r="K73" s="5">
+        <v>125</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G74" s="5">
+        <v>202</v>
+      </c>
+      <c r="H74" s="5">
+        <v>207</v>
+      </c>
+      <c r="I74" s="4">
+        <v>76.8</v>
+      </c>
+      <c r="J74" s="4">
+        <v>89.95</v>
+      </c>
+      <c r="K74" s="5">
+        <v>144</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G75" s="5">
+        <v>174</v>
+      </c>
+      <c r="H75" s="5">
+        <v>297</v>
+      </c>
+      <c r="I75" s="4">
+        <v>95.68</v>
+      </c>
+      <c r="J75" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="K75" s="5">
+        <v>149</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" s="5">
+        <v>177</v>
+      </c>
+      <c r="H76" s="5">
+        <v>219</v>
+      </c>
+      <c r="I76" s="4">
+        <v>90.68</v>
+      </c>
+      <c r="J76" s="4">
+        <v>94.78</v>
+      </c>
+      <c r="K76" s="5">
+        <v>148</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="5">
+        <v>239</v>
+      </c>
+      <c r="H77" s="5">
+        <v>285</v>
+      </c>
+      <c r="I77" s="4">
+        <v>95.7</v>
+      </c>
+      <c r="J77" s="4">
+        <v>85.17</v>
+      </c>
+      <c r="K77" s="5">
+        <v>127</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G78" s="5">
+        <v>346</v>
+      </c>
+      <c r="H78" s="5">
+        <v>248</v>
+      </c>
+      <c r="I78" s="4">
+        <v>98.68</v>
+      </c>
+      <c r="J78" s="4">
+        <v>37.28</v>
+      </c>
+      <c r="K78" s="5">
+        <v>123</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G79" s="5">
+        <v>311</v>
+      </c>
+      <c r="H79" s="5">
+        <v>160</v>
+      </c>
+      <c r="I79" s="4">
+        <v>94</v>
+      </c>
+      <c r="J79" s="4">
+        <v>63.13</v>
+      </c>
+      <c r="K79" s="5">
+        <v>142</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="5">
+        <v>226</v>
+      </c>
+      <c r="H80" s="5">
+        <v>285</v>
+      </c>
+      <c r="I80" s="4">
+        <v>75.430000000000007</v>
+      </c>
+      <c r="J80" s="4">
+        <v>66.56</v>
+      </c>
+      <c r="K80" s="5">
+        <v>131</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G81" s="5">
+        <v>342</v>
+      </c>
+      <c r="H81" s="5">
+        <v>256</v>
+      </c>
+      <c r="I81" s="4">
+        <v>76.55</v>
+      </c>
+      <c r="J81" s="4">
+        <v>66.290000000000006</v>
+      </c>
+      <c r="K81" s="5">
+        <v>120</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G82" s="5">
+        <v>271</v>
+      </c>
+      <c r="H82" s="5">
+        <v>176</v>
+      </c>
+      <c r="I82" s="4">
+        <v>96.38</v>
+      </c>
+      <c r="J82" s="4">
+        <v>50.56</v>
+      </c>
+      <c r="K82" s="5">
+        <v>176</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="5">
+        <v>347</v>
+      </c>
+      <c r="H83" s="5">
+        <v>172</v>
+      </c>
+      <c r="I83" s="4">
+        <v>79.11</v>
+      </c>
+      <c r="J83" s="4">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="K83" s="5">
+        <v>130</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G84" s="5">
+        <v>321</v>
+      </c>
+      <c r="H84" s="5">
+        <v>278</v>
+      </c>
+      <c r="I84" s="4">
+        <v>99.17</v>
+      </c>
+      <c r="J84" s="4">
+        <v>72.48</v>
+      </c>
+      <c r="K84" s="5">
+        <v>217</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="5">
+        <v>225</v>
+      </c>
+      <c r="H85" s="5">
+        <v>288</v>
+      </c>
+      <c r="I85" s="4">
+        <v>82.19</v>
+      </c>
+      <c r="J85" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="K85" s="5">
+        <v>155</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G86" s="5">
+        <v>301</v>
+      </c>
+      <c r="H86" s="5">
+        <v>274</v>
+      </c>
+      <c r="I86" s="4">
+        <v>75.89</v>
+      </c>
+      <c r="J86" s="4">
+        <v>82.78</v>
+      </c>
+      <c r="K86" s="5">
+        <v>138</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G87" s="5">
+        <v>173</v>
+      </c>
+      <c r="H87" s="5">
+        <v>318</v>
+      </c>
+      <c r="I87" s="4">
+        <v>87.76</v>
+      </c>
+      <c r="J87" s="4">
+        <v>79.12</v>
+      </c>
+      <c r="K87" s="5">
+        <v>126</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G88" s="5">
+        <v>275</v>
+      </c>
+      <c r="H88" s="5">
+        <v>286</v>
+      </c>
+      <c r="I88" s="4">
+        <v>79.849999999999994</v>
+      </c>
+      <c r="J88" s="4">
+        <v>88.84</v>
+      </c>
+      <c r="K88" s="5">
+        <v>222</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G89" s="5">
+        <v>214</v>
+      </c>
+      <c r="H89" s="5">
+        <v>222</v>
+      </c>
+      <c r="I89" s="4">
+        <v>96.45</v>
+      </c>
+      <c r="J89" s="4">
+        <v>56.03</v>
+      </c>
+      <c r="K89" s="5">
+        <v>131</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G90" s="5">
+        <v>279</v>
+      </c>
+      <c r="H90" s="5">
+        <v>286</v>
+      </c>
+      <c r="I90" s="4">
+        <v>99.23</v>
+      </c>
+      <c r="J90" s="4">
+        <v>51.57</v>
+      </c>
+      <c r="K90" s="5">
+        <v>222</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G91" s="5">
+        <v>330</v>
+      </c>
+      <c r="H91" s="5">
+        <v>318</v>
+      </c>
+      <c r="I91" s="4">
+        <v>98.12</v>
+      </c>
+      <c r="J91" s="4">
+        <v>52.83</v>
+      </c>
+      <c r="K91" s="5">
+        <v>199</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G92" s="5">
+        <v>187</v>
+      </c>
+      <c r="H92" s="5">
+        <v>185</v>
+      </c>
+      <c r="I92" s="4">
+        <v>98.24</v>
+      </c>
+      <c r="J92" s="4">
+        <v>80.239999999999995</v>
+      </c>
+      <c r="K92" s="5">
+        <v>166</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G93" s="5">
+        <v>219</v>
+      </c>
+      <c r="H93" s="5">
+        <v>191</v>
+      </c>
+      <c r="I93" s="4">
+        <v>76.510000000000005</v>
+      </c>
+      <c r="J93" s="4">
+        <v>68.52</v>
+      </c>
+      <c r="K93" s="5">
+        <v>163</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="5">
+        <v>299</v>
+      </c>
+      <c r="H94" s="5">
+        <v>246</v>
+      </c>
+      <c r="I94" s="4">
+        <v>96.99</v>
+      </c>
+      <c r="J94" s="4">
+        <v>54.53</v>
+      </c>
+      <c r="K94" s="5">
+        <v>131</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G95" s="5">
+        <v>266</v>
+      </c>
+      <c r="H95" s="5">
+        <v>315</v>
+      </c>
+      <c r="I95" s="4">
+        <v>76.180000000000007</v>
+      </c>
+      <c r="J95" s="4">
+        <v>83.65</v>
+      </c>
+      <c r="K95" s="5">
+        <v>121</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G96" s="5">
+        <v>151</v>
+      </c>
+      <c r="H96" s="5">
+        <v>178</v>
+      </c>
+      <c r="I96" s="4">
+        <v>84.4</v>
+      </c>
+      <c r="J96" s="4">
+        <v>43.23</v>
+      </c>
+      <c r="K96" s="5">
+        <v>122</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G97" s="5">
+        <v>321</v>
+      </c>
+      <c r="H97" s="5">
+        <v>172</v>
+      </c>
+      <c r="I97" s="4">
+        <v>76.13</v>
+      </c>
+      <c r="J97" s="4">
+        <v>99.93</v>
+      </c>
+      <c r="K97" s="5">
+        <v>124</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G98" s="5">
+        <v>295</v>
+      </c>
+      <c r="H98" s="5">
+        <v>346</v>
+      </c>
+      <c r="I98" s="4">
+        <v>83.12</v>
+      </c>
+      <c r="J98" s="4">
+        <v>49.93</v>
+      </c>
+      <c r="K98" s="5">
+        <v>202</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G99" s="5">
+        <v>297</v>
+      </c>
+      <c r="H99" s="5">
+        <v>261</v>
+      </c>
+      <c r="I99" s="4">
+        <v>93.44</v>
+      </c>
+      <c r="J99" s="4">
+        <v>91.63</v>
+      </c>
+      <c r="K99" s="5">
+        <v>218</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G100" s="5">
+        <v>314</v>
+      </c>
+      <c r="H100" s="5">
+        <v>259</v>
+      </c>
+      <c r="I100" s="4">
+        <v>87.58</v>
+      </c>
+      <c r="J100" s="4">
+        <v>57.97</v>
+      </c>
+      <c r="K100" s="5">
+        <v>168</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G101" s="5">
+        <v>215</v>
+      </c>
+      <c r="H101" s="5">
+        <v>240</v>
+      </c>
+      <c r="I101" s="4">
+        <v>98.46</v>
+      </c>
+      <c r="J101" s="4">
+        <v>57.41</v>
+      </c>
+      <c r="K101" s="5">
+        <v>148</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G102" s="5">
+        <v>217</v>
+      </c>
+      <c r="H102" s="5">
+        <v>284</v>
+      </c>
+      <c r="I102" s="4">
+        <v>82.31</v>
+      </c>
+      <c r="J102" s="4">
+        <v>67.02</v>
+      </c>
+      <c r="K102" s="5">
+        <v>177</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="5">
+        <v>225</v>
+      </c>
+      <c r="H103" s="5">
+        <v>299</v>
+      </c>
+      <c r="I103" s="4">
+        <v>85.8</v>
+      </c>
+      <c r="J103" s="4">
+        <v>69.12</v>
+      </c>
+      <c r="K103" s="5">
+        <v>173</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G104" s="5">
+        <v>288</v>
+      </c>
+      <c r="H104" s="5">
+        <v>241</v>
+      </c>
+      <c r="I104" s="4">
+        <v>87.25</v>
+      </c>
+      <c r="J104" s="4">
+        <v>59.88</v>
+      </c>
+      <c r="K104" s="5">
+        <v>180</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G105" s="5">
+        <v>156</v>
+      </c>
+      <c r="H105" s="5">
+        <v>302</v>
+      </c>
+      <c r="I105" s="4">
+        <v>98.67</v>
+      </c>
+      <c r="J105" s="4">
+        <v>63.51</v>
+      </c>
+      <c r="K105" s="5">
+        <v>139</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G106" s="5">
+        <v>324</v>
+      </c>
+      <c r="H106" s="5">
+        <v>295</v>
+      </c>
+      <c r="I106" s="4">
+        <v>89.41</v>
+      </c>
+      <c r="J106" s="4">
+        <v>60.24</v>
+      </c>
+      <c r="K106" s="5">
+        <v>125</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="46.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G107" s="5">
+        <v>241</v>
+      </c>
+      <c r="H107" s="5">
+        <v>187</v>
+      </c>
+      <c r="I107" s="4">
+        <v>86.14</v>
+      </c>
+      <c r="J107" s="4">
+        <v>94.02</v>
+      </c>
+      <c r="K107" s="5">
+        <v>135</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
